--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6503.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6503.xlsx
@@ -1280,6 +1280,9 @@
           <t>6503-04-04-FG</t>
         </is>
       </c>
+      <c r="H14" t="n">
+        <v>0.43</v>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>6503-04-04-FG</t>
@@ -1292,12 +1295,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-04-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-04-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL@BORE = Air-Way per-size tap drill -04 0.43 (A1)</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1317,6 +1320,9 @@
           <t>6503-06-06-FG</t>
         </is>
       </c>
+      <c r="H15" t="n">
+        <v>0.57</v>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>6503-06-06-FG</t>
@@ -1329,12 +1335,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1354,6 +1360,9 @@
           <t>6503-12-12-FG</t>
         </is>
       </c>
+      <c r="H16" t="n">
+        <v>0.91</v>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>6503-12-12-FG</t>
@@ -1366,12 +1375,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1391,6 +1400,9 @@
           <t>6503-16-16-FG</t>
         </is>
       </c>
+      <c r="H17" t="n">
+        <v>1.14</v>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>6503-16-16-FG</t>
@@ -1403,12 +1415,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL@BORE = Air-Way per-size tap drill -16 1.14 (A1)</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">

--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6503.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6503.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R17"/>
+  <dimension ref="A1:S17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +509,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1280,6 +1285,9 @@
           <t>6503-04-04-FG</t>
         </is>
       </c>
+      <c r="C14" t="n">
+        <v>1.18</v>
+      </c>
       <c r="H14" t="n">
         <v>0.43</v>
       </c>
@@ -1295,12 +1303,12 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-04-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: M5@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-04-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL@BORE = Air-Way per-size tap drill -04 0.43 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6503-04-04-FG (PARTcommunity / CADENAS, M5@DRIVE=M6; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -04 0.43 (A1)</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1311,6 +1319,11 @@
       <c r="R14" t="inlineStr">
         <is>
           <t>6503-04-04-FG</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1320,6 +1333,9 @@
           <t>6503-06-06-FG</t>
         </is>
       </c>
+      <c r="C15" t="n">
+        <v>1.38</v>
+      </c>
       <c r="H15" t="n">
         <v>0.57</v>
       </c>
@@ -1335,12 +1351,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: M5@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6503-06-06-FG (PARTcommunity / CADENAS, M5@DRIVE=M6; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1351,6 +1367,11 @@
       <c r="R15" t="inlineStr">
         <is>
           <t>6503-06-06-FG</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1360,6 +1381,9 @@
           <t>6503-12-12-FG</t>
         </is>
       </c>
+      <c r="C16" t="n">
+        <v>1.86</v>
+      </c>
       <c r="H16" t="n">
         <v>0.91</v>
       </c>
@@ -1375,12 +1399,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: M5@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6503-12-12-FG (PARTcommunity / CADENAS, M5@DRIVE=M6; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1391,6 +1415,11 @@
       <c r="R16" t="inlineStr">
         <is>
           <t>6503-12-12-FG</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6503.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_6503.xlsx
@@ -1285,12 +1285,33 @@
           <t>6503-04-04-FG</t>
         </is>
       </c>
+      <c r="B14" t="n">
+        <v>0.88</v>
+      </c>
       <c r="C14" t="n">
         <v>1.18</v>
       </c>
+      <c r="D14" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.172</v>
+      </c>
       <c r="H14" t="n">
         <v>0.43</v>
       </c>
+      <c r="I14" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.4375</v>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>6503-04-04-FG</t>
@@ -1298,17 +1319,17 @@
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: M5@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-04-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: M5@DRIVE, N1@DRIVE, M10@DRIVE, C3HEX@HEX, Y1@HEX, D@BORE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-04-04 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6503-04-04-FG (PARTcommunity / CADENAS, M5@DRIVE=M6; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -04 0.43 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-04-04 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6503-04-04-FG (PARTcommunity / CADENAS, M5@DRIVE=M6, N1@DRIVE=M2, M10@DRIVE=M4, C3HEX@HEX=C, Y1@HEX=Y, D@BORE=BD, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -04 0.43 (A1)</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1333,12 +1354,33 @@
           <t>6503-06-06-FG</t>
         </is>
       </c>
+      <c r="B15" t="n">
+        <v>1.02</v>
+      </c>
       <c r="C15" t="n">
         <v>1.38</v>
       </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.297</v>
+      </c>
       <c r="H15" t="n">
         <v>0.57</v>
       </c>
+      <c r="I15" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.5625</v>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>6503-06-06-FG</t>
@@ -1346,17 +1388,17 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: M5@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: M5@DRIVE, N1@DRIVE, M10@DRIVE, C3HEX@HEX, Y1@HEX, D@BORE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-06-06 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6503-06-06-FG (PARTcommunity / CADENAS, M5@DRIVE=M6; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-06-06 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6503-06-06-FG (PARTcommunity / CADENAS, M5@DRIVE=M6, N1@DRIVE=M2, M10@DRIVE=M4, C3HEX@HEX=C, Y1@HEX=Y, D@BORE=BD, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -06 0.57 (A1)</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1381,12 +1423,33 @@
           <t>6503-12-12-FG</t>
         </is>
       </c>
+      <c r="B16" t="n">
+        <v>1.36</v>
+      </c>
       <c r="C16" t="n">
         <v>1.86</v>
       </c>
+      <c r="D16" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.609</v>
+      </c>
       <c r="H16" t="n">
         <v>0.91</v>
       </c>
+      <c r="I16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.0625</v>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>6503-12-12-FG</t>
@@ -1394,17 +1457,17 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: M5@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL@BORE] [BRENNAN-CAD 2026-10-21: M5@DRIVE, N1@DRIVE, M10@DRIVE, C3HEX@HEX, Y1@HEX, D@BORE, THDMAJ_A@DRIVE, THDMAJ_B@DRIVE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 6503-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6503-12-12-FG (PARTcommunity / CADENAS, M5@DRIVE=M6; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 6503-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | Brennan CAD record 6503-12-12-FG (PARTcommunity / CADENAS, M5@DRIVE=M6, N1@DRIVE=M2, M10@DRIVE=M4, C3HEX@HEX=C, Y1@HEX=Y, D@BORE=BD, THDMAJ_A@DRIVE=ATHD, THDMAJ_B@DRIVE=BTHD; user 2026-10-21 "yes you can use them following my rule") | TAPDRILL@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
